--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484693_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484693_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9551</v>
+        <v>8.492800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8151</v>
+        <v>7.7739</v>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>0.7189</v>
       </c>
       <c r="G2" t="n">
         <v>3.6191</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2418</v>
+        <v>0.7796</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5664</v>
+        <v>0.5253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6755</v>
+        <v>0.2543</v>
       </c>
       <c r="V2" t="n">
         <v>3.1778</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6325</v>
+        <v>7.8936</v>
       </c>
       <c r="E3" t="n">
-        <v>10.247</v>
+        <v>9.5328</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6144</v>
+        <v>-1.6392</v>
       </c>
       <c r="G3" t="n">
         <v>5.5314</v>
@@ -688,13 +688,13 @@
         <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8342</v>
+        <v>1.0952</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4827</v>
+        <v>0.7685</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3515</v>
+        <v>0.3267</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.973</v>
+        <v>4.0632</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3682</v>
+        <v>2.6567</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6047</v>
+        <v>1.4065</v>
       </c>
       <c r="G4" t="n">
         <v>3.4966</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0157</v>
+        <v>0.106</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0558</v>
+        <v>0.2327</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.1267</v>
       </c>
       <c r="V4" t="n">
         <v>0.6439</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.481</v>
+        <v>3.3819</v>
       </c>
       <c r="E5" t="n">
         <v>1.798</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6831</v>
+        <v>1.584</v>
       </c>
       <c r="G5" t="n">
         <v>0.486</v>
@@ -844,13 +844,13 @@
         <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.6968</v>
       </c>
       <c r="T5" t="n">
         <v>0.5302</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2657</v>
+        <v>0.1666</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6281</v>
+        <v>2.8422</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5276</v>
+        <v>1.8161</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1005</v>
+        <v>1.0262</v>
       </c>
       <c r="G6" t="n">
         <v>4.5381</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.177</v>
+        <v>0.0371</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0558</v>
+        <v>0.2327</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1212</v>
+        <v>-0.1955</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6335</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3731</v>
+        <v>1.6127</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1726</v>
+        <v>0.1149</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2005</v>
+        <v>1.4978</v>
       </c>
       <c r="G7" t="n">
         <v>3.6344</v>
@@ -1000,13 +1000,13 @@
         <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0398</v>
+        <v>0.2794</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8673</v>
+        <v>0.8096</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8275</v>
+        <v>-0.5302</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5681</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1157</v>
+        <v>1.4319</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2208</v>
+        <v>0.4131</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8949</v>
+        <v>1.0188</v>
       </c>
       <c r="G8" t="n">
         <v>0.905</v>
@@ -1078,13 +1078,13 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5222</v>
+        <v>-0.2061</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.302</v>
+        <v>-0.1782</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8079</v>
+        <v>1.0655</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2952</v>
+        <v>0.7595</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4874</v>
+        <v>0.306</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5031</v>
+        <v>1.1027</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5929</v>
+        <v>-0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0897</v>
+        <v>1.2019</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2682</v>
+        <v>2.4707</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1333</v>
+        <v>1.0121</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1349</v>
+        <v>1.4586</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.765</v>
+        <v>-1.368</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5404</v>
+        <v>-1.1113</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2246</v>
+        <v>-0.2567</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7</v>
+        <v>0.2064</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6214</v>
+        <v>0.365</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0786</v>
+        <v>-0.1586</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5785</v>
+        <v>1.5889</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3038</v>
+        <v>0.4288</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3199</v>
+        <v>1.9657</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0161</v>
+        <v>-1.5369</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1027</v>
+        <v>1.5031</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0992</v>
+        <v>1.5929</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2019</v>
+        <v>-0.0897</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4707</v>
+        <v>2.2682</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0121</v>
+        <v>2.1333</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4586</v>
+        <v>0.1349</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.368</v>
+        <v>-0.765</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1113</v>
+        <v>-0.5404</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2567</v>
+        <v>-0.2246</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5553</v>
+        <v>0.3209</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0746</v>
+        <v>0.2919</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4806</v>
+        <v>0.029</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5889</v>
+        <v>-1.5785</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.133</v>
+        <v>-1.5258</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4407</v>
+        <v>-0.8087</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6923</v>
+        <v>-0.7171</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4838</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.144</v>
+        <v>0.4632</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2391</v>
+        <v>0.3929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0951</v>
+        <v>0.0703</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8847</v>
+        <v>-2.4753</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0379</v>
+        <v>-1.6533</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8468</v>
+        <v>-0.822</v>
       </c>
       <c r="G13" t="n">
         <v>-1.237</v>
@@ -1468,13 +1468,13 @@
         <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5144</v>
+        <v>-0.105</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3122</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2022</v>
+        <v>-0.1774</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2328</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.0867</v>
+        <v>-2.7706</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7259</v>
+        <v>-1.5336</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3609</v>
+        <v>-1.237</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0307</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9619</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6867</v>
+        <v>-0.5628</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9109</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.79090000000001</v>
+        <v>25.066</v>
       </c>
       <c r="E15" t="n">
-        <v>23.185</v>
+        <v>23.46019999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6058</v>
+        <v>1.605999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>22.69</v>
@@ -1606,7 +1606,7 @@
         <v>11.8626</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.810600000000001</v>
+        <v>-5.810599999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-6.289499999999999</v>
@@ -1615,7 +1615,7 @@
         <v>0.4789</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9162000000000001</v>
+        <v>0.9161999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-16.4933</v>
@@ -1624,19 +1624,19 @@
         <v>17.4093</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7526</v>
+        <v>3.0278</v>
       </c>
       <c r="T15" t="n">
-        <v>3.835</v>
+        <v>4.110300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0823</v>
+        <v>-1.0825</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5681</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3422</v>
+        <v>7.342200000000001</v>
       </c>
       <c r="X15" t="n">
         <v>-8.910400000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2509</v>
+        <v>1.4957</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6002</v>
+        <v>1.6964</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3493</v>
+        <v>-0.2007</v>
       </c>
       <c r="G17" t="n">
         <v>0.9769</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0925</v>
+        <v>-0.8477</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6056</v>
+        <v>-0.5094</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4869</v>
+        <v>-0.3382</v>
       </c>
       <c r="V17" t="n">
         <v>0.6335</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0381</v>
+        <v>1.2305</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6655</v>
+        <v>3.8578</v>
       </c>
       <c r="F18" t="n">
         <v>-2.6273</v>
@@ -1858,10 +1858,10 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5867</v>
+        <v>-0.3944</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1855</v>
+        <v>0.0068</v>
       </c>
       <c r="U18" t="n">
         <v>-0.4012</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3577</v>
+        <v>-0.5093</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1306</v>
+        <v>1.2267</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4883</v>
+        <v>-1.736</v>
       </c>
       <c r="G20" t="n">
         <v>1.6967</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2926</v>
+        <v>-0.4442</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0746</v>
+        <v>-0.1731</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5785</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8053</v>
+        <v>-0.6766</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1121</v>
+        <v>0.3217</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6931</v>
+        <v>-0.9983</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3989</v>
+        <v>-2.6598</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.309</v>
+        <v>-2.5991</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0899</v>
+        <v>-0.0608</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2417</v>
+        <v>-0.4754</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3993</v>
+        <v>-1.152</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.641</v>
+        <v>0.6766</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1572</v>
+        <v>-2.1845</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7083</v>
+        <v>-1.4471</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4489</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>0.133</v>
+        <v>0.3339</v>
       </c>
       <c r="T21" t="n">
-        <v>0.402</v>
+        <v>0.4751</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.269</v>
+        <v>-0.1412</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6439</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0534</v>
+        <v>-0.728</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4475</v>
+        <v>-0.2083</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6059</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6598</v>
+        <v>-1.3989</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5991</v>
+        <v>-0.309</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0608</v>
+        <v>-1.0899</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4754</v>
+        <v>-0.2417</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.152</v>
+        <v>0.3993</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6766</v>
+        <v>-0.641</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1845</v>
+        <v>-1.1572</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4471</v>
+        <v>-0.7083</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.4489</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6493</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0429</v>
+        <v>0.2102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2941</v>
+        <v>0.3058</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7488</v>
+        <v>-0.0956</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0.6439</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1429</v>
+        <v>-1.7801</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0317</v>
+        <v>-0.7432</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1112</v>
+        <v>-1.0369</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6737</v>
@@ -2248,13 +2248,13 @@
         <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6654</v>
+        <v>-0.3026</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3492</v>
+        <v>-0.0607</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3162</v>
+        <v>-0.2419</v>
       </c>
       <c r="V23" t="n">
         <v>2.212</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5944</v>
+        <v>-2.9047</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0198</v>
+        <v>-0.789</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5747</v>
+        <v>-2.1157</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8626</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5797</v>
+        <v>0.2694</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2806</v>
+        <v>0.5113</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7008</v>
+        <v>-0.2419</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1515</v>
+        <v>-2.9155</v>
       </c>
       <c r="E25" t="n">
         <v>0.2613</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4128</v>
+        <v>-3.1768</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6258</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1573</v>
+        <v>0.3933</v>
       </c>
       <c r="T25" t="n">
         <v>0.4374</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2801</v>
+        <v>-0.0441</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9658</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7088</v>
+        <v>-3.8871</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.2388</v>
+        <v>-2.2879</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.47</v>
+        <v>-1.5992</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.1737</v>
+        <v>-5.2955</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.7504</v>
+        <v>-1.1252</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.4233</v>
+        <v>-4.1703</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.0381</v>
+        <v>-1.9097</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.4804</v>
+        <v>0.5294</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5577</v>
+        <v>-2.4391</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.1356</v>
+        <v>-3.3858</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.27</v>
+        <v>-1.6546</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8656</v>
+        <v>-1.7312</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8314</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9879</v>
+        <v>0.4702</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1566</v>
+        <v>0.0927</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.5785</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6439</v>
+        <v>1.9005</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.2629</v>
+        <v>-3.9041</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.5763</v>
+        <v>-2.7196</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.6865</v>
+        <v>-1.1845</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.2955</v>
+        <v>-4.1737</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1252</v>
+        <v>-2.7504</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.1703</v>
+        <v>-1.4233</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.9097</v>
+        <v>-2.0381</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5294</v>
+        <v>-1.4804</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.4391</v>
+        <v>-0.5577</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.3858</v>
+        <v>-2.1356</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.6546</v>
+        <v>-1.27</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.7312</v>
+        <v>-0.8656</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R27" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1872</v>
+        <v>0.6361</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1818</v>
+        <v>0.5072</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0054</v>
+        <v>0.129</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5785</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.9005</v>
+        <v>0.6439</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.4207</v>
+        <v>-4.2968</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1473</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.2734</v>
+        <v>-4.1495</v>
       </c>
       <c r="G28" t="n">
         <v>-1.7355</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.0358</v>
+        <v>-0.9119</v>
       </c>
       <c r="T28" t="n">
         <v>-0.5324</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5034</v>
+        <v>-0.3795</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.8331</v>
+        <v>-6.2425</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.9407</v>
+        <v>-4.3253</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8924</v>
+        <v>-1.9172</v>
       </c>
       <c r="G29" t="n">
         <v>-5.5413</v>
@@ -2716,13 +2716,13 @@
         <v>1.4661</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0747</v>
+        <v>-0.3346</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1267</v>
+        <v>-0.2579</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-24.791</v>
+        <v>-22.8678</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.605899999999999</v>
+        <v>-1.606</v>
       </c>
       <c r="F30" t="n">
-        <v>-23.1849</v>
+        <v>-21.2618</v>
       </c>
       <c r="G30" t="n">
         <v>-22.69</v>
@@ -2770,10 +2770,10 @@
         <v>5.8108</v>
       </c>
       <c r="K30" t="n">
-        <v>6.289500000000001</v>
+        <v>6.289500000000002</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4789000000000001</v>
+        <v>-0.4789</v>
       </c>
       <c r="M30" t="n">
         <v>-28.5009</v>
@@ -2785,7 +2785,7 @@
         <v>-11.8627</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.9163000000000001</v>
+        <v>-0.9163000000000003</v>
       </c>
       <c r="Q30" t="n">
         <v>-17.4097</v>
@@ -2794,13 +2794,13 @@
         <v>16.4931</v>
       </c>
       <c r="S30" t="n">
-        <v>-2.7526</v>
+        <v>-0.8294999999999999</v>
       </c>
       <c r="T30" t="n">
         <v>1.0823</v>
       </c>
       <c r="U30" t="n">
-        <v>-3.835</v>
+        <v>-1.9117</v>
       </c>
       <c r="V30" t="n">
         <v>1.5682</v>
